--- a/DEVELOPMENT_ALL_OLD_NEW/TOMMY HILFIGER/TH.00046 MEDIUM WASH .xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/TOMMY HILFIGER/TH.00046 MEDIUM WASH .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\TC.DEVELOPMENT.BRAND FILE 2\TOMMY HILFIGER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\TOMMY HILFIGER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB9086E-7DAF-4BA9-9877-463D9D524CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B69477-544F-49D1-ACAC-AB070D1EE881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1717,47 +1717,26 @@
     <xf numFmtId="164" fontId="25" fillId="5" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1771,6 +1750,247 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="5" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="35" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="24" fillId="5" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1787,18 +2007,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="25" fillId="6" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1823,221 +2031,13 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="55" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="56" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="5" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="35" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2337,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M112"/>
@@ -3135,21 +3135,21 @@
       <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="187">
+      <c r="C2" s="136">
         <v>45933</v>
       </c>
-      <c r="D2" s="188"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="190" t="s">
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="191"/>
-      <c r="H2" s="192" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="192"/>
-      <c r="J2" s="192"/>
-      <c r="K2" s="193"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
@@ -3158,19 +3158,19 @@
       <c r="B3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="187" t="s">
+      <c r="C3" s="136" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="188"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="213" t="s">
+      <c r="D3" s="137"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="214"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="175"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="167"/>
+      <c r="K3" s="168"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
@@ -3179,17 +3179,17 @@
       <c r="B4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="199"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="196"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="144"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="177"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="163"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="170"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
@@ -3198,17 +3198,17 @@
       <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="198">
+      <c r="C5" s="147">
         <v>5135003</v>
       </c>
-      <c r="D5" s="199"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="197"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="144"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="164"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="164"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
@@ -3217,13 +3217,13 @@
       <c r="B6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="204" t="s">
+      <c r="C6" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="205"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="197"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="146"/>
       <c r="H6" s="83"/>
       <c r="I6" s="84"/>
       <c r="J6" s="83"/>
@@ -3236,13 +3236,13 @@
       <c r="B7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="204" t="s">
+      <c r="C7" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="205"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="197"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="146"/>
       <c r="H7" s="83"/>
       <c r="I7" s="84"/>
       <c r="J7" s="83"/>
@@ -3255,17 +3255,17 @@
       <c r="B8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="201" t="s">
+      <c r="C8" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="202"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="197"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="143"/>
-      <c r="K8" s="144"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="146"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="163"/>
+      <c r="K8" s="164"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
@@ -3274,17 +3274,17 @@
       <c r="B9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="204" t="s">
+      <c r="C9" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="205"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="197"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="142"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="142"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="146"/>
+      <c r="H9" s="161"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="162"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
@@ -3293,15 +3293,15 @@
       <c r="B10" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="207"/>
-      <c r="D10" s="208"/>
-      <c r="E10" s="209"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="197"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="164"/>
-      <c r="K10" s="165"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="146"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="166"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -3310,15 +3310,15 @@
       <c r="B11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="210"/>
-      <c r="D11" s="211"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="142"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="161"/>
+      <c r="K11" s="162"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
@@ -3327,15 +3327,15 @@
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="197"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="144"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="146"/>
+      <c r="H12" s="163"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="163"/>
+      <c r="K12" s="164"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
@@ -3344,15 +3344,15 @@
       <c r="B13" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="131"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="197"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="144"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="146"/>
+      <c r="H13" s="163"/>
+      <c r="I13" s="164"/>
+      <c r="J13" s="163"/>
+      <c r="K13" s="164"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
@@ -3361,13 +3361,13 @@
       <c r="B14" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="196"/>
-      <c r="G14" s="197"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="142"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="161"/>
+      <c r="I14" s="162"/>
       <c r="J14" s="16"/>
       <c r="K14" s="14"/>
       <c r="L14" s="2"/>
@@ -3378,17 +3378,17 @@
       <c r="B15" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="203" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="138"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="140" t="s">
+      <c r="D15" s="204"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="140"/>
-      <c r="H15" s="140"/>
-      <c r="I15" s="140"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="206"/>
+      <c r="I15" s="206"/>
       <c r="J15" s="17"/>
       <c r="K15" s="15"/>
       <c r="L15" s="2"/>
@@ -3406,14 +3406,14 @@
       <c r="E16" s="19">
         <v>1</v>
       </c>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="166" t="s">
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="206"/>
+      <c r="I16" s="206"/>
+      <c r="J16" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="172" t="s">
+      <c r="K16" s="184" t="s">
         <v>12</v>
       </c>
       <c r="L16" s="2"/>
@@ -3439,12 +3439,12 @@
       <c r="G17" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="166" t="s">
+      <c r="H17" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="173"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="182"/>
+      <c r="K17" s="185"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
@@ -3453,15 +3453,15 @@
       <c r="B18" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="215" t="s">
+      <c r="C18" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="216"/>
-      <c r="E18" s="216"/>
-      <c r="F18" s="216"/>
-      <c r="G18" s="216"/>
-      <c r="H18" s="216"/>
-      <c r="I18" s="217"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
       <c r="J18" s="56"/>
       <c r="K18" s="104"/>
       <c r="L18" s="5"/>
@@ -3472,13 +3472,13 @@
       <c r="B19" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="145"/>
-      <c r="D19" s="146"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="146"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="146"/>
-      <c r="I19" s="147"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="209"/>
       <c r="J19" s="90"/>
       <c r="K19" s="85"/>
       <c r="L19" s="5"/>
@@ -3489,13 +3489,13 @@
       <c r="B20" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="148"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="150"/>
+      <c r="C20" s="210"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211"/>
+      <c r="F20" s="211"/>
+      <c r="G20" s="211"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="212"/>
       <c r="J20" s="90"/>
       <c r="K20" s="85"/>
       <c r="L20" s="5"/>
@@ -3536,10 +3536,10 @@
       <c r="G22" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="151" t="s">
+      <c r="H22" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="152"/>
+      <c r="I22" s="214"/>
       <c r="J22" s="90"/>
       <c r="K22" s="85"/>
       <c r="L22" s="5"/>
@@ -3557,10 +3557,10 @@
       <c r="G23" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="151" t="s">
+      <c r="H23" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="I23" s="152"/>
+      <c r="I23" s="214"/>
       <c r="J23" s="90"/>
       <c r="K23" s="85"/>
       <c r="L23" s="5"/>
@@ -3578,10 +3578,10 @@
       <c r="G24" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="151" t="s">
+      <c r="H24" s="213" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="152"/>
+      <c r="I24" s="214"/>
       <c r="J24" s="90"/>
       <c r="K24" s="85"/>
       <c r="L24" s="5"/>
@@ -3607,10 +3607,10 @@
       <c r="G25" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="151" t="s">
+      <c r="H25" s="213" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="152"/>
+      <c r="I25" s="214"/>
       <c r="J25" s="90"/>
       <c r="K25" s="85"/>
       <c r="L25" s="5"/>
@@ -3624,8 +3624,8 @@
       <c r="E26" s="98"/>
       <c r="F26" s="99"/>
       <c r="G26" s="99"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="154"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="192"/>
       <c r="J26" s="99"/>
       <c r="K26" s="99"/>
       <c r="L26" s="5"/>
@@ -3651,10 +3651,10 @@
       <c r="G27" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="155" t="s">
+      <c r="H27" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="155"/>
+      <c r="I27" s="183"/>
       <c r="J27" s="85"/>
       <c r="K27" s="85"/>
       <c r="L27" s="5"/>
@@ -3676,8 +3676,8 @@
       </c>
       <c r="F28" s="56"/>
       <c r="G28" s="56"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
       <c r="J28" s="85"/>
       <c r="K28" s="85"/>
       <c r="L28" s="5"/>
@@ -3695,8 +3695,8 @@
       <c r="E29" s="56"/>
       <c r="F29" s="56"/>
       <c r="G29" s="56"/>
-      <c r="H29" s="124"/>
-      <c r="I29" s="124"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
       <c r="J29" s="85"/>
       <c r="K29" s="85"/>
       <c r="L29" s="5"/>
@@ -3733,10 +3733,10 @@
       <c r="G31" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="124" t="s">
+      <c r="H31" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="124"/>
+      <c r="I31" s="132"/>
       <c r="J31" s="90"/>
       <c r="K31" s="96"/>
       <c r="L31" s="5"/>
@@ -3762,10 +3762,10 @@
       <c r="G32" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="125" t="s">
+      <c r="H32" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="I32" s="125"/>
+      <c r="I32" s="135"/>
       <c r="J32" s="57"/>
       <c r="K32" s="101"/>
       <c r="L32" s="5"/>
@@ -3783,8 +3783,8 @@
       <c r="E33" s="67"/>
       <c r="F33" s="65"/>
       <c r="G33" s="97"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="127"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="134"/>
       <c r="J33" s="65"/>
       <c r="K33" s="65"/>
       <c r="L33" s="5"/>
@@ -3793,11 +3793,11 @@
     <row r="34" spans="1:13" ht="73.95" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="73"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="123"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="217"/>
       <c r="H34" s="91"/>
       <c r="I34" s="95"/>
       <c r="J34" s="66"/>
@@ -3821,10 +3821,10 @@
       <c r="G35" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H35" s="124" t="s">
+      <c r="H35" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="124"/>
+      <c r="I35" s="132"/>
       <c r="J35" s="90"/>
       <c r="K35" s="96"/>
       <c r="L35" s="5"/>
@@ -3842,10 +3842,10 @@
       <c r="G36" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H36" s="125" t="s">
+      <c r="H36" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="I36" s="125"/>
+      <c r="I36" s="135"/>
       <c r="J36" s="57"/>
       <c r="K36" s="101"/>
       <c r="L36" s="5"/>
@@ -3867,8 +3867,8 @@
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="97"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="127"/>
+      <c r="H37" s="133"/>
+      <c r="I37" s="134"/>
       <c r="J37" s="65"/>
       <c r="K37" s="65"/>
       <c r="L37" s="5"/>
@@ -3882,8 +3882,8 @@
       <c r="E38" s="73"/>
       <c r="F38" s="73"/>
       <c r="G38" s="66"/>
-      <c r="H38" s="128"/>
-      <c r="I38" s="129"/>
+      <c r="H38" s="194"/>
+      <c r="I38" s="195"/>
       <c r="J38" s="66"/>
       <c r="K38" s="66"/>
       <c r="L38" s="5"/>
@@ -3909,10 +3909,10 @@
       <c r="G39" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="126" t="s">
+      <c r="H39" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="I39" s="127"/>
+      <c r="I39" s="134"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65"/>
       <c r="L39" s="5"/>
@@ -3938,10 +3938,10 @@
       <c r="G40" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="126" t="s">
+      <c r="H40" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="I40" s="127"/>
+      <c r="I40" s="134"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65"/>
       <c r="L40" s="5"/>
@@ -3982,10 +3982,10 @@
       <c r="G42" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="126" t="s">
+      <c r="H42" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="I42" s="127"/>
+      <c r="I42" s="134"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65"/>
       <c r="L42" s="5"/>
@@ -4011,10 +4011,10 @@
       <c r="G43" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="H43" s="126" t="s">
+      <c r="H43" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="I43" s="127"/>
+      <c r="I43" s="134"/>
       <c r="J43" s="65"/>
       <c r="K43" s="65"/>
       <c r="L43" s="5"/>
@@ -4028,8 +4028,8 @@
       <c r="E44" s="73"/>
       <c r="F44" s="73"/>
       <c r="G44" s="66"/>
-      <c r="H44" s="128"/>
-      <c r="I44" s="129"/>
+      <c r="H44" s="194"/>
+      <c r="I44" s="195"/>
       <c r="J44" s="66"/>
       <c r="K44" s="66"/>
       <c r="L44" s="5"/>
@@ -4055,10 +4055,10 @@
       <c r="G45" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="H45" s="171" t="s">
+      <c r="H45" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="I45" s="171"/>
+      <c r="I45" s="131"/>
       <c r="J45" s="65"/>
       <c r="K45" s="65"/>
       <c r="L45" s="5"/>
@@ -4084,10 +4084,10 @@
       <c r="G46" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="171" t="s">
+      <c r="H46" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="I46" s="171"/>
+      <c r="I46" s="131"/>
       <c r="J46" s="65"/>
       <c r="K46" s="65"/>
       <c r="L46" s="5"/>
@@ -4098,10 +4098,11 @@
       <c r="B47" s="68"/>
       <c r="C47" s="98"/>
       <c r="D47" s="98"/>
+      <c r="E47" s="98"/>
       <c r="F47" s="99"/>
       <c r="G47" s="99"/>
-      <c r="H47" s="153"/>
-      <c r="I47" s="154"/>
+      <c r="H47" s="191"/>
+      <c r="I47" s="192"/>
       <c r="J47" s="99"/>
       <c r="K47" s="99"/>
       <c r="L47" s="5"/>
@@ -4118,7 +4119,7 @@
       <c r="D48" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="98">
+      <c r="E48" s="67">
         <v>60</v>
       </c>
       <c r="F48" s="57">
@@ -4127,10 +4128,10 @@
       <c r="G48" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="155" t="s">
+      <c r="H48" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="I48" s="155"/>
+      <c r="I48" s="183"/>
       <c r="J48" s="85"/>
       <c r="K48" s="85"/>
       <c r="L48" s="5"/>
@@ -4146,8 +4147,8 @@
       <c r="E49" s="56"/>
       <c r="F49" s="56"/>
       <c r="G49" s="56"/>
-      <c r="H49" s="124"/>
-      <c r="I49" s="124"/>
+      <c r="H49" s="132"/>
+      <c r="I49" s="132"/>
       <c r="J49" s="85"/>
       <c r="K49" s="85"/>
       <c r="L49" s="5"/>
@@ -4188,10 +4189,10 @@
       <c r="G51" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="H51" s="163" t="s">
+      <c r="H51" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="163"/>
+      <c r="I51" s="130"/>
       <c r="J51" s="57"/>
       <c r="K51" s="57"/>
       <c r="L51" s="5"/>
@@ -4217,10 +4218,10 @@
       <c r="G52" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="H52" s="163" t="s">
+      <c r="H52" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="I52" s="163"/>
+      <c r="I52" s="130"/>
       <c r="J52" s="57"/>
       <c r="K52" s="57"/>
       <c r="L52" s="5"/>
@@ -4229,11 +4230,11 @@
     <row r="53" spans="1:13" ht="64.95" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="52"/>
-      <c r="C53" s="130"/>
-      <c r="D53" s="130"/>
-      <c r="E53" s="130"/>
-      <c r="F53" s="130"/>
-      <c r="G53" s="130"/>
+      <c r="C53" s="199"/>
+      <c r="D53" s="199"/>
+      <c r="E53" s="199"/>
+      <c r="F53" s="199"/>
+      <c r="G53" s="199"/>
       <c r="H53" s="54"/>
       <c r="I53" s="54"/>
       <c r="J53" s="53"/>
@@ -4251,8 +4252,8 @@
       <c r="E54" s="60"/>
       <c r="F54" s="61"/>
       <c r="G54" s="62"/>
-      <c r="H54" s="162"/>
-      <c r="I54" s="162"/>
+      <c r="H54" s="186"/>
+      <c r="I54" s="186"/>
       <c r="J54" s="57"/>
       <c r="K54" s="57"/>
       <c r="L54" s="5"/>
@@ -4272,10 +4273,10 @@
       <c r="G55" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H55" s="163" t="s">
+      <c r="H55" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="I55" s="163"/>
+      <c r="I55" s="130"/>
       <c r="J55" s="57"/>
       <c r="K55" s="57"/>
       <c r="L55" s="5"/>
@@ -4293,10 +4294,10 @@
       <c r="G56" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="163" t="s">
+      <c r="H56" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="I56" s="163"/>
+      <c r="I56" s="130"/>
       <c r="J56" s="57"/>
       <c r="K56" s="57"/>
       <c r="L56" s="5"/>
@@ -4314,10 +4315,10 @@
       <c r="G57" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H57" s="163" t="s">
+      <c r="H57" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="I57" s="163"/>
+      <c r="I57" s="130"/>
       <c r="J57" s="57"/>
       <c r="K57" s="57"/>
       <c r="L57" s="5"/>
@@ -4331,8 +4332,8 @@
       <c r="E58" s="98"/>
       <c r="F58" s="99"/>
       <c r="G58" s="99"/>
-      <c r="H58" s="153"/>
-      <c r="I58" s="170"/>
+      <c r="H58" s="191"/>
+      <c r="I58" s="193"/>
       <c r="J58" s="66"/>
       <c r="K58" s="106"/>
       <c r="L58" s="5"/>
@@ -4358,10 +4359,10 @@
       <c r="G59" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H59" s="155" t="s">
+      <c r="H59" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="I59" s="155"/>
+      <c r="I59" s="183"/>
       <c r="J59" s="57"/>
       <c r="K59" s="101"/>
       <c r="L59" s="5"/>
@@ -4381,8 +4382,8 @@
       <c r="E60" s="56"/>
       <c r="F60" s="57"/>
       <c r="G60" s="57"/>
-      <c r="H60" s="186"/>
-      <c r="I60" s="186"/>
+      <c r="H60" s="181"/>
+      <c r="I60" s="181"/>
       <c r="J60" s="57"/>
       <c r="K60" s="101"/>
       <c r="L60" s="5"/>
@@ -4423,10 +4424,10 @@
       <c r="G62" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="179" t="s">
+      <c r="H62" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="I62" s="179"/>
+      <c r="I62" s="172"/>
       <c r="J62" s="28"/>
       <c r="K62" s="28"/>
       <c r="L62" s="5"/>
@@ -4444,10 +4445,10 @@
       <c r="G63" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H63" s="169" t="s">
+      <c r="H63" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="I63" s="169"/>
+      <c r="I63" s="190"/>
       <c r="J63" s="28"/>
       <c r="K63" s="28"/>
       <c r="L63" s="5"/>
@@ -4467,8 +4468,8 @@
       <c r="E64" s="26"/>
       <c r="F64" s="25"/>
       <c r="G64" s="25"/>
-      <c r="H64" s="182"/>
-      <c r="I64" s="182"/>
+      <c r="H64" s="176"/>
+      <c r="I64" s="176"/>
       <c r="J64" s="25"/>
       <c r="K64" s="25"/>
       <c r="L64" s="5"/>
@@ -4509,10 +4510,10 @@
       <c r="G66" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="H66" s="167" t="s">
+      <c r="H66" s="188" t="s">
         <v>45</v>
       </c>
-      <c r="I66" s="168"/>
+      <c r="I66" s="189"/>
       <c r="J66" s="57"/>
       <c r="K66" s="74"/>
       <c r="L66" s="5"/>
@@ -4532,10 +4533,10 @@
       <c r="G67" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="H67" s="185" t="s">
+      <c r="H67" s="180" t="s">
         <v>33</v>
       </c>
-      <c r="I67" s="185"/>
+      <c r="I67" s="180"/>
       <c r="J67" s="57"/>
       <c r="K67" s="57"/>
       <c r="L67" s="5"/>
@@ -4549,8 +4550,8 @@
       <c r="E68" s="34"/>
       <c r="F68" s="32"/>
       <c r="G68" s="26"/>
-      <c r="H68" s="183"/>
-      <c r="I68" s="184"/>
+      <c r="H68" s="178"/>
+      <c r="I68" s="179"/>
       <c r="J68" s="35"/>
       <c r="K68" s="35"/>
       <c r="L68" s="5"/>
@@ -4564,8 +4565,8 @@
       <c r="E69" s="26"/>
       <c r="F69" s="31"/>
       <c r="G69" s="31"/>
-      <c r="H69" s="160"/>
-      <c r="I69" s="160"/>
+      <c r="H69" s="177"/>
+      <c r="I69" s="177"/>
       <c r="J69" s="32"/>
       <c r="K69" s="33"/>
       <c r="L69" s="5"/>
@@ -4579,8 +4580,8 @@
       <c r="E70" s="26"/>
       <c r="F70" s="31"/>
       <c r="G70" s="31"/>
-      <c r="H70" s="160"/>
-      <c r="I70" s="160"/>
+      <c r="H70" s="177"/>
+      <c r="I70" s="177"/>
       <c r="J70" s="32"/>
       <c r="K70" s="33"/>
       <c r="L70" s="5"/>
@@ -4594,8 +4595,8 @@
       <c r="E71" s="26"/>
       <c r="F71" s="31"/>
       <c r="G71" s="31"/>
-      <c r="H71" s="157"/>
-      <c r="I71" s="157"/>
+      <c r="H71" s="173"/>
+      <c r="I71" s="173"/>
       <c r="J71" s="32"/>
       <c r="K71" s="33"/>
       <c r="L71" s="5"/>
@@ -4609,8 +4610,8 @@
       <c r="E72" s="34"/>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
-      <c r="H72" s="180"/>
-      <c r="I72" s="181"/>
+      <c r="H72" s="174"/>
+      <c r="I72" s="175"/>
       <c r="J72" s="32"/>
       <c r="K72" s="33"/>
       <c r="L72" s="5"/>
@@ -4624,8 +4625,8 @@
       <c r="E73" s="34"/>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
-      <c r="H73" s="178"/>
-      <c r="I73" s="178"/>
+      <c r="H73" s="171"/>
+      <c r="I73" s="171"/>
       <c r="J73" s="31"/>
       <c r="K73" s="40"/>
       <c r="L73" s="5"/>
@@ -4639,8 +4640,8 @@
       <c r="E74" s="31"/>
       <c r="F74" s="31"/>
       <c r="G74" s="31"/>
-      <c r="H74" s="160"/>
-      <c r="I74" s="160"/>
+      <c r="H74" s="177"/>
+      <c r="I74" s="177"/>
       <c r="J74" s="31"/>
       <c r="K74" s="40"/>
       <c r="L74" s="5"/>
@@ -4654,8 +4655,8 @@
       <c r="E75" s="31"/>
       <c r="F75" s="31"/>
       <c r="G75" s="31"/>
-      <c r="H75" s="158"/>
-      <c r="I75" s="159"/>
+      <c r="H75" s="197"/>
+      <c r="I75" s="198"/>
       <c r="J75" s="31"/>
       <c r="K75" s="40"/>
       <c r="L75" s="2"/>
@@ -4669,8 +4670,8 @@
       <c r="E76" s="31"/>
       <c r="F76" s="31"/>
       <c r="G76" s="31"/>
-      <c r="H76" s="160"/>
-      <c r="I76" s="160"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
       <c r="J76" s="43"/>
       <c r="K76" s="40"/>
       <c r="L76" s="2"/>
@@ -4684,8 +4685,8 @@
       <c r="E77" s="31"/>
       <c r="F77" s="31"/>
       <c r="G77" s="31"/>
-      <c r="H77" s="157"/>
-      <c r="I77" s="157"/>
+      <c r="H77" s="173"/>
+      <c r="I77" s="173"/>
       <c r="J77" s="43"/>
       <c r="K77" s="40"/>
       <c r="L77" s="2"/>
@@ -4699,8 +4700,8 @@
       <c r="E78" s="25"/>
       <c r="F78" s="25"/>
       <c r="G78" s="25"/>
-      <c r="H78" s="161"/>
-      <c r="I78" s="161"/>
+      <c r="H78" s="187"/>
+      <c r="I78" s="187"/>
       <c r="J78" s="45"/>
       <c r="K78" s="46"/>
       <c r="L78" s="2"/>
@@ -4714,8 +4715,8 @@
       <c r="E79" s="25"/>
       <c r="F79" s="25"/>
       <c r="G79" s="25"/>
-      <c r="H79" s="161"/>
-      <c r="I79" s="161"/>
+      <c r="H79" s="187"/>
+      <c r="I79" s="187"/>
       <c r="J79" s="45"/>
       <c r="K79" s="46"/>
       <c r="L79" s="2"/>
@@ -4729,8 +4730,8 @@
       <c r="E80" s="25"/>
       <c r="F80" s="25"/>
       <c r="G80" s="25"/>
-      <c r="H80" s="161"/>
-      <c r="I80" s="161"/>
+      <c r="H80" s="187"/>
+      <c r="I80" s="187"/>
       <c r="J80" s="45"/>
       <c r="K80" s="46"/>
       <c r="L80" s="2"/>
@@ -4744,8 +4745,8 @@
       <c r="E81" s="25"/>
       <c r="F81" s="25"/>
       <c r="G81" s="25"/>
-      <c r="H81" s="161"/>
-      <c r="I81" s="161"/>
+      <c r="H81" s="187"/>
+      <c r="I81" s="187"/>
       <c r="J81" s="45"/>
       <c r="K81" s="46"/>
       <c r="L81" s="2"/>
@@ -4759,8 +4760,8 @@
       <c r="E82" s="49"/>
       <c r="F82" s="49"/>
       <c r="G82" s="49"/>
-      <c r="H82" s="156"/>
-      <c r="I82" s="156"/>
+      <c r="H82" s="196"/>
+      <c r="I82" s="196"/>
       <c r="J82" s="50"/>
       <c r="K82" s="51"/>
       <c r="L82" s="2"/>
@@ -4906,16 +4907,76 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:I16"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -4932,84 +4993,24 @@
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:I16"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H32:I32"/>
     <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
     <mergeCell ref="H37:I37"/>
     <mergeCell ref="H38:I38"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="11" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="12" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>